--- a/daily_matches/job_matches_2026-03-17.xlsx
+++ b/daily_matches/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Operations Analytics Data Scientist</t>
+          <t>Senior Data Scientist - Fraud/Risk</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, AWS SageMaker, GCP Vertex AI</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, XGBoost, LightGBM, Azure ML, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=b60a2339618be99f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>AI/ML Engineer - Agentic</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Pinecone, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB</t>
+          <t>RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,102 +531,102 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
+          <t>https://www.indeed.com/viewjob?jk=af5d15c7ab669f27</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Software Engineer, (.NET)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Foundation Source</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, PySpark</t>
+          <t>RAG, S3, EC2, Docker, CI/CD, Jenkins, Git, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342faa6b5c9756a2</t>
+          <t>https://www.indeed.com/viewjob?jk=8d566d00eb2e403d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>ROLLER</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, Kafka, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
+          <t>https://www.indeed.com/viewjob?jk=214a2ff977f27118</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>DEV OPS ENGINEER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New York University</t>
+          <t>Z Supply</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL</t>
+          <t>Generative AI, RAG, S3, Docker, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44061aea5dff945c</t>
+          <t>https://www.indeed.com/viewjob?jk=af0dfce8372b998d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SAP Successfactors iXp Intern - Software Developer - SUMMER 2026</t>
+          <t>AI &amp; Automation Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>CSW Industrials</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R</t>
+          <t>RAG, Azure ML, CI/CD, Git, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10eb17e618d5ca1d</t>
+          <t>https://www.indeed.com/viewjob?jk=02a6f1e734dc88f1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer, AI Enablement</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Manchester, CT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,567 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d51db2029f8a1ddc</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Athena, Redshift, Databricks, Redshift, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SS&amp;C</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Waltham, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, S3, MongoDB, Cassandra, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ffdd714376fc122</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior BE Software Engineer (Remote)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Autofi</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Git, MySQL, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e23cbf6ed42f1ceb</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Software AI SME</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Teledyne FLIR</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Huntsville, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LangChain, Copilot, Hugging Face, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85c531d3a322741f</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Backend Software Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>DualEntry</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, AKS, CI/CD, PostgreSQL, Cassandra, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8bbaf6a2bccfb07d</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SAS</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=38b2be41415df8a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DATA SCIENTIST</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Dollar General</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Goodlettsville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, Git, Databricks, PySpark, Tableau, Matplotlib, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c81ccc2c8f052915</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AI Data Scientist</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Git, Snowflake, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6c3f0ee12cb8f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Systems Software Engineer - Hardware Tools and Infrastructure</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Durham, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>FastAPI, Kubernetes, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a0a48c37eaeefc0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Blackhawk Network</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Coppell, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Terraform, PostgreSQL, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5803d2acd25ade2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CPI Security</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, S3, CI/CD, Snowflake, Tableau, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Data Scientist – Merchandising &amp; Inventory Machine Learning - Hybrid – Seattle, WA</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Nordstrom</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=abc1931299f711f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Supply Chain Machine Learning Data Scientist - Hybrid - Seattle, WA</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Nordstrom</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90d15f0c343878e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Data Scientist, Analytics - Performance</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Discord</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, SQL, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd537c30a6b16ef1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Software Development Engineer I</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Optimum</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Bethpage, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c73a56f3755de7a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Software Development Engineer I</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Optimum</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Bethpage, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2f8c317a65b59d1</t>
+          <t>https://www.indeed.com/viewjob?jk=225bf2d46c0fb4a6</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-17.xlsx
+++ b/daily_matches/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Fraud/Risk</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Lyzr AI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>30</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, XGBoost, LightGBM, Azure ML, Git, Snowflake, Databricks</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, S3, EC2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b60a2339618be99f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a23265f32b23de3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Agentic</t>
+          <t>Software Engineer III: Machine Learning Platform</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af5d15c7ab669f27</t>
+          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, (.NET)</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Foundation Source</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, Jenkins, Git, MySQL, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d566d00eb2e403d</t>
+          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Compliance - Quant Modeling Senior Associate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ROLLER</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, XGBoost, LightGBM, CatBoost, AKS, Git, Databricks, Matplotlib, Seaborn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=214a2ff977f27118</t>
+          <t>https://www.indeed.com/viewjob?jk=20aa926eab32416e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DEV OPS ENGINEER</t>
+          <t>Senior Software Engineer (Backend)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Z Supply</t>
+          <t>archer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Docker, CI/CD, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, Terraform, Git, Kafka, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0dfce8372b998d</t>
+          <t>https://www.indeed.com/viewjob?jk=4892f5075126af15</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI &amp; Automation Engineer (Hybrid)</t>
+          <t>AI Platform Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CSW Industrials</t>
+          <t>SymphonyAI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, CI/CD, Git, Python, SQL, R, Java, Optimization</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,182 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a6f1e734dc88f1</t>
+          <t>https://www.indeed.com/viewjob?jk=e727c510ae6ee71c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Manchester, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sr. Associate, Software Development Engineer in ATM Test</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santander Consumer Bank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Quincy, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15a7cc27ea9afce9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Information Retrieval Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Mistral, FAISS, Pinecone, Docker, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95f6c4b130b8d9a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=225bf2d46c0fb4a6</t>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3c4f6954c0f5910</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI Orchestrator)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cotiviti</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a11162ab0ecd108</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-17.xlsx
+++ b/daily_matches/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lyzr AI</t>
+          <t>Tapouts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Venice, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, S3, EC2</t>
+          <t>Data Scientist, Redshift, BigQuery, Data Lake, Apache Airflow, Snowflake, BigQuery, Redshift, Kafka, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a23265f32b23de3</t>
+          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III: Machine Learning Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>Data Scientist, RAG, Dataflow, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Sr Eng, AI Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>PENNYMAC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Snowflake</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, spaCy, S3, EC2, BigQuery, BigQuery, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
+          <t>https://www.indeed.com/viewjob?jk=339bfe8490029591</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Compliance - Quant Modeling Senior Associate</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, LightGBM, CatBoost, AKS, Git, Databricks, Matplotlib, Seaborn</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20aa926eab32416e</t>
+          <t>https://www.indeed.com/viewjob?jk=cca45c9a3eb1d292</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Backend)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>archer</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bridgeton, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, Terraform, Git, Kafka, PostgreSQL, Python, SQL</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4892f5075126af15</t>
+          <t>https://www.indeed.com/viewjob?jk=ef17b59d1b779ca6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Platform Architect</t>
+          <t>Consultant – Java</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SymphonyAI</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Python, R</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e727c510ae6ee71c</t>
+          <t>https://www.indeed.com/viewjob?jk=2778ae536c75ec45</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,87 +696,87 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java, Scala</t>
+          <t>RAG, Jenkins, Terraform, Git, Snowflake, Databricks, PySpark, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Associate, Software Development Engineer in ATM Test</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Santander Consumer Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+          <t>RAG, Pinecone, FastAPI, Docker, Git, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a7cc27ea9afce9</t>
+          <t>https://www.indeed.com/viewjob?jk=86f8b9bc4836d990</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Information Retrieval Engineer</t>
+          <t>Software Engineer Intern - Summer 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Mistral, FAISS, Pinecone, Docker, Python, R, Scala</t>
+          <t>Data Scientist, RAG, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95f6c4b130b8d9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4c9badd066b1eb19</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>Nucs AI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, MySQL, Python, SQL, R, Java</t>
+          <t>RAG, FastAPI, Kubernetes, CI/CD, Terraform, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c4f6954c0f5910</t>
+          <t>https://www.indeed.com/viewjob?jk=355f6d743973c414</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Orchestrator)</t>
+          <t>LLM Deployment Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,122 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab30e3f8a7f9dc91</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior AI Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84c6034b2543af31</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a11162ab0ecd108</t>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fa0b3c6d64f75a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Teradata</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93d5887e867c8762</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-17.xlsx
+++ b/daily_matches/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tapouts</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Venice, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, BigQuery, Data Lake, Apache Airflow, Snowflake, BigQuery, Redshift, Kafka, Python</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, Pinecone, MLflow, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Dataflow, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, SQL</t>
+          <t>Data Scientist, RAG, Docker, CI/CD, Jenkins, Terraform, Git, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,427 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Sr Eng, AI Platform</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PENNYMAC</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Westlake Village, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, spaCy, S3, EC2, BigQuery, BigQuery, Python</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=339bfe8490029591</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Teradata</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cca45c9a3eb1d292</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bridgeton, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, CI/CD, Jenkins, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef17b59d1b779ca6</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Consultant – Java</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Genpact</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, R, Java</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2778ae536c75ec45</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Jenkins, Terraform, Git, Snowflake, Databricks, PySpark, NoSQL, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Full Stack Software Developer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Pinecone, FastAPI, Docker, Git, PostgreSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86f8b9bc4836d990</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Software Engineer Intern - Summer 2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Exact Sciences</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c9badd066b1eb19</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Nucs AI</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, Kubernetes, CI/CD, Terraform, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=355f6d743973c414</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>LLM Deployment Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab30e3f8a7f9dc91</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior AI Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84c6034b2543af31</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa0b3c6d64f75a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Teradata</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93d5887e867c8762</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-17.xlsx
+++ b/daily_matches/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, Pinecone, MLflow, Docker, Kubernetes, Git</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,42 +496,1337 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
+          <t>https://www.indeed.com/viewjob?jk=ddbe4c5dca694294</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, Kafka, Cassandra</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kafka Real Time Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, Kafka, Cassandra</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Kafka Real Time Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, Kafka, Cassandra</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Global</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Vantage Data Centers</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PostgreSQL, Power BI</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Kafka Support Analyst</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Redshift, Git, Snowflake, Databricks, Redshift, Kafka, Hadoop, MySQL, Cassandra, NoSQL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Streaming Data</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, Snowflake, Databricks, PySpark, Kafka, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sr. Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ISPOT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>14.4</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Docker, CI/CD, Jenkins, Terraform, Git, Databricks, PySpark, Python</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Data Lake, CI/CD, Snowflake, MySQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c574e4f3a8dfe2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, S3, EC2, Glue, Athena, Terraform, Python</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a246f2fce8506457</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, S3, EC2, Glue, Athena, Terraform, Python</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbf17f38d746779a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Streaming Data</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Terraform, Redshift, Python, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Surescripts</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git, Snowflake, Databricks, NoSQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66a598c2cd89c1c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cloud-Native MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Data Lake, Apache Airflow, CI/CD, Terraform, Hadoop, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Associate ML Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, FAISS, Snowflake, Kafka, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=757126cb415fa4ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, S3, EC2, Glue, Athena, Terraform, Python, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=838425ec33e5fff1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, FAISS, Snowflake, Kafka, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3b669fd4735a001</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer-AI</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Thomson Reuters</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sr. SW Engineer- Generative AI</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, Python, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b15ea5b7549b8351</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer New</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Chantilly, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Hadoop, PostgreSQL, MySQL, NoSQL, Tableau, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8000eecc255c25b</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=200b55a5030b830e</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer – Local LLM &amp; Custom RAG Systems</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NEOnet</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Cuyahoga Falls, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79aa27ac9c288f42</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>KNOTCH, INC.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Git, Snowflake, Python, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8dd10ce832f4515a</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Spring/Spring Boot Architect</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e62470d61b3dfe4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03037f396bed2071</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b82dd62fa0e8493f</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer - .Net</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, MongoDB, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99374436e879f2d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Waters</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Milford, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fda6bdf1c5291df4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Alarm.com</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Lawrence, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2aa317c750470ba8</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Python Architect</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Copilot, FastAPI, Docker, Kubernetes, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b2aa3971822bc3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Vector Database Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, FastAPI, CI/CD, PostgreSQL, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3353efb5f91eff0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ab518c07e5c4bd4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Vector Database Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, FastAPI, CI/CD, PostgreSQL, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8aef487788fbe3b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=674b77e8965ca088</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2b411ce63f39481</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=919e9963c156e59a</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>LLM Deployment Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f80ce9f4fa83c827</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=10e7254f043f98d7</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-17.xlsx
+++ b/daily_matches/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, FastAPI</t>
+          <t>RAG, S3, Glue, Redshift, BigQuery, Synapse, Data Lake, Kinesis, Dataflow, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddbe4c5dca694294</t>
+          <t>https://www.indeed.com/viewjob?jk=31ac562fdbccfcbb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Machine Learning Engineer – Generative AI (Remote)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, Kafka, Cassandra</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, BigQuery, CI/CD, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
+          <t>https://www.indeed.com/viewjob?jk=9356b62004fa5a43</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Data Engineer (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, Kafka, Cassandra</t>
+          <t>RAG, Docker, CI/CD, Snowflake, Databricks, PySpark, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
+          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Open Lending</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, Kafka, Cassandra</t>
+          <t>Data Scientist, RAG, XGBoost, MLflow, Databricks, PySpark, Polars, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=980979d9074d5784</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Open Lending</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PostgreSQL, Power BI</t>
+          <t>Data Scientist, RAG, XGBoost, MLflow, Databricks, PySpark, Polars, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=46dca6f38ea157d1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Redshift, Git, Snowflake, Databricks, Redshift, Kafka, Hadoop, MySQL, Cassandra, NoSQL</t>
+          <t>RAG, S3, Athena, Redshift, BigQuery, BigQuery, Redshift, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, CI/CD, Snowflake, Databricks, PySpark, Kafka, Python, SQL</t>
+          <t>RAG, S3, Athena, Redshift, BigQuery, BigQuery, Redshift, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Data Lake, CI/CD, Snowflake, MySQL, Python, SQL, R</t>
+          <t>Machine Learning Engineer, Hadoop, PostgreSQL, MySQL, NoSQL, Tableau, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c574e4f3a8dfe2d</t>
+          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, S3, EC2, Glue, Athena, Terraform, Python</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a246f2fce8506457</t>
+          <t>https://www.indeed.com/viewjob?jk=c00e725f72169245</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goodwill Industries of Ky., Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, S3, EC2, Glue, Athena, Terraform, Python</t>
+          <t>RAG, Copilot, Synapse, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf17f38d746779a</t>
+          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Terraform, Redshift, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea3f0ee7726aea</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Machine Learning Engineer II – Generative AI (Remote)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git, Snowflake, Databricks, NoSQL</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66a598c2cd89c1c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b7591a2efbcb284e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Application Developer &amp; Database Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, Apache Airflow, CI/CD, Terraform, Hadoop, Python, SQL</t>
+          <t>RAG, TensorFlow, PyTorch, MongoDB, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
+          <t>https://www.indeed.com/viewjob?jk=20577dc3fbb13487</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>(USA) Senior, Data Scientist - Digital Twin Systems Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, LangChain, RAG, TensorFlow, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
+          <t>https://www.indeed.com/viewjob?jk=03211c91f3b22020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>RESEARCH PROGRAMMER II (SOFTWARE ENGINEER) - C. Wu Lab</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scripps Research</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, FAISS, Snowflake, Kafka, Tableau, Python, SQL, R</t>
+          <t>RAG, S3, Docker, CI/CD, Git, MongoDB, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757126cb415fa4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=221139d1ca13c5ae</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>RESEARCH PROGRAMMER III - C. Wu Lab</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scripps Research</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, S3, EC2, Glue, Athena, Terraform, Python, R</t>
+          <t>RAG, S3, Docker, CI/CD, Git, MongoDB, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=838425ec33e5fff1</t>
+          <t>https://www.indeed.com/viewjob?jk=cd81839948841963</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Front-End Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mochi Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, FAISS, Snowflake, Kafka, Tableau, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, Git, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b669fd4735a001</t>
+          <t>https://www.indeed.com/viewjob?jk=9cb603e90c260feb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-AI</t>
+          <t>Sr. Backend Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Mochi Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
+          <t>https://www.indeed.com/viewjob?jk=9289a85d40da1d93</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer- Generative AI</t>
+          <t>Senior Software Engineer- Enrichment</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, Python, R</t>
+          <t>LangChain, BigQuery, Docker, Git, BigQuery, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b15ea5b7549b8351</t>
+          <t>https://www.indeed.com/viewjob?jk=423a67caac16e54c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer New</t>
+          <t>Senior Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1143,15 +1143,15 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Hadoop, PostgreSQL, MySQL, NoSQL, Tableau, Python, SQL, R, Java</t>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+          <t>https://www.indeed.com/viewjob?jk=3ea96fc38c6bacb5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Cheminformatics Data Scientist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lubrizol</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wickliffe, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+          <t>Data Scientist, Generative AI, TensorFlow, XGBoost, Azure ML, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,637 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8000eecc255c25b</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=200b55a5030b830e</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer – Local LLM &amp; Custom RAG Systems</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>NEOnet</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Cuyahoga Falls, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79aa27ac9c288f42</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>KNOTCH, INC.</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Git, Snowflake, Python, R</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd10ce832f4515a</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Spring/Spring Boot Architect</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e62470d61b3dfe4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AI Engineer, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03037f396bed2071</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>AI Engineer, Prompt Engineering, Kubernetes, AKS, CI/CD, Terraform, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b82dd62fa0e8493f</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Software Engineer - .Net</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, MongoDB, NoSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99374436e879f2d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>AI Engineer Intern</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Waters</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Milford, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fda6bdf1c5291df4</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Alarm.com</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Lawrence, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa317c750470ba8</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Python Architect</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Copilot, FastAPI, Docker, Kubernetes, Git, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b2aa3971822bc3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Vector Database Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, FastAPI, CI/CD, PostgreSQL, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3353efb5f91eff0b</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Kubernetes MLOps Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Terraform, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab518c07e5c4bd4</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Vector Database Engineer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, FastAPI, CI/CD, PostgreSQL, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8aef487788fbe3b0</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ML Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=674b77e8965ca088</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Kubernetes MLOps Engineer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Terraform, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2b411ce63f39481</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>ML Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=919e9963c156e59a</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>LLM Deployment Engineer</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f80ce9f4fa83c827</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>EXL Service</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=10e7254f043f98d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d28ac8f700721df7</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-17.xlsx
+++ b/daily_matches/job_matches_2026-03-17.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, BigQuery, Synapse, Data Lake, Kinesis, Dataflow, Terraform</t>
+          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ac562fdbccfcbb</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer – Generative AI (Remote)</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, BigQuery, CI/CD, BigQuery, Python, SQL</t>
+          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9356b62004fa5a43</t>
+          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer (No Sponsorship Available)</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Snowflake, Databricks, PySpark, Tableau, Python, SQL, R</t>
+          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
+          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Junior Software Development Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Open Lending</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, MLflow, Databricks, PySpark, Polars, Tableau, Power BI, Python</t>
+          <t>RAG, Azure ML, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Jenkins, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=980979d9074d5784</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AI Engineer (Full Stack) - R&amp;D IT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Open Lending</t>
+          <t>Driscoll's</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Watsonville, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, MLflow, Databricks, PySpark, Polars, Tableau, Power BI, Python</t>
+          <t>AI Engineer, RAG, Copilot, FastAPI, Docker, CI/CD, Git, PostgreSQL, MySQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46dca6f38ea157d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c304f375d2956f85</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Zywave, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, Athena, Redshift, BigQuery, BigQuery, Redshift, Tableau, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Git, Tableau, Matplotlib, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8ebb87b0666c5e6d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Athena, Redshift, BigQuery, BigQuery, Redshift, Tableau, Python, SQL</t>
+          <t>RAG, BigQuery, Synapse, CI/CD, Git, Snowflake, BigQuery, Tableau, Power BI, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Hadoop, PostgreSQL, MySQL, NoSQL, Tableau, Python, SQL, R, Java</t>
+          <t>RAG, Glue, Athena, Redshift, Databricks, Redshift, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
+          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Haystack TV</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00e725f72169245</t>
+          <t>https://www.indeed.com/viewjob?jk=924dace8a553fcc2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Goodwill Industries of Ky., Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Synapse, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, EC2, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
+          <t>https://www.indeed.com/viewjob?jk=7b046656a7cdd501</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Senior Engineer AI and Machine Learning</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Aurora, CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, LLaMA, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea3f0ee7726aea</t>
+          <t>https://www.indeed.com/viewjob?jk=0ff0cfb22a83b3c4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II – Generative AI (Remote)</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Glue, Redshift, Data Lake, CI/CD, Git, Redshift, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7591a2efbcb284e</t>
+          <t>https://www.indeed.com/viewjob?jk=50effdd5410c6590</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Application Developer &amp; Database Engineer</t>
+          <t>Senior Commercial Data Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bonterra</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, MongoDB, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, AKS, Git, Tableau, Power BI, Quicksight, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20577dc3fbb13487</t>
+          <t>https://www.indeed.com/viewjob?jk=a8de79a6d9da6728</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Scientist - Digital Twin Systems Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, TensorFlow, Git, Python, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Git, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03211c91f3b22020</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1566b51c5ab7b9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RESEARCH PROGRAMMER II (SOFTWARE ENGINEER) - C. Wu Lab</t>
+          <t>Data Intern</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Scripps Research</t>
+          <t>CNX</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Canonsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, Git, MongoDB, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, Data Lake, Git, Snowflake, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=221139d1ca13c5ae</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5cfd4d75c45f55</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RESEARCH PROGRAMMER III - C. Wu Lab</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Scripps Research</t>
+          <t>Avaya</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, Git, MongoDB, Python, R, Java, Scala</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd81839948841963</t>
+          <t>https://www.indeed.com/viewjob?jk=93cc248964e1485d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Front-End Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mochi Health</t>
+          <t>EasyPost</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Kubernetes, Git, Kafka, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cb603e90c260feb</t>
+          <t>https://www.indeed.com/viewjob?jk=23d6509dfd302acb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer</t>
+          <t>Graduate Engineer, Design Automation, Front-End &amp; AI Driven Methodologies</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mochi Health</t>
+          <t>Arm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
+          <t>Generative AI, TensorFlow, PyTorch, AKS, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9289a85d40da1d93</t>
+          <t>https://www.indeed.com/viewjob?jk=7dc49d90bae64d48</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Enrichment</t>
+          <t>Software Integration Engineer 3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LangChain, BigQuery, Docker, Git, BigQuery, NoSQL, Python, SQL, R</t>
+          <t>Docker, CI/CD, Git, Hadoop, MongoDB, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423a67caac16e54c</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5cea9e989f2b26</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test (SDET)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ea96fc38c6bacb5</t>
+          <t>https://www.indeed.com/viewjob?jk=3fceeafafff1abbc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cheminformatics Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lubrizol</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wickliffe, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, TensorFlow, XGBoost, Azure ML, Git, Python, R, Optimization</t>
+          <t>Data Scientist, CI/CD, Databricks, Kafka, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d28ac8f700721df7</t>
+          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-17.xlsx
+++ b/daily_matches/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
+          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Junior Software Development Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>23.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Jenkins, Git</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
+          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer (Full Stack) - R&amp;D IT</t>
+          <t>Senior Software Engineer (ServiceNow)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Driscoll's</t>
+          <t>Hotwire Communications</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Watsonville, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>23.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, FastAPI, Docker, CI/CD, Git, PostgreSQL, MySQL, Python</t>
+          <t>Generative AI, RAG, Prompt Engineering, S3, EC2, Kinesis, Docker, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c304f375d2956f85</t>
+          <t>https://www.indeed.com/viewjob?jk=8a28cfe9183e3c37</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Zywave, Inc.</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Git, Tableau, Matplotlib, Seaborn, Python, SQL</t>
+          <t>Data Scientist, RAG, Synapse, CI/CD, Git, Databricks, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ebb87b0666c5e6d</t>
+          <t>https://www.indeed.com/viewjob?jk=e53c61ac50aad63e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
+          <t>AI Platform Engineer - Associate</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Synapse, CI/CD, Git, Snowflake, BigQuery, Tableau, Power BI, SQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Cortex, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
+          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Data Engineer Palantir</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Glue, Athena, Redshift, Databricks, Redshift, Tableau, Python, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, S3, Glue, Athena, Redshift, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
+          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Haystack TV</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Snowflake, Python, SQL, R</t>
+          <t>MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, Cassandra, Tableau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=924dace8a553fcc2</t>
+          <t>https://www.indeed.com/viewjob?jk=c906675f7a065e47</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Kissimmee, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, XGBoost, LightGBM, BigQuery, Git, Snowflake, BigQuery, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b046656a7cdd501</t>
+          <t>https://www.indeed.com/viewjob?jk=6e3d8c3773cd2c8c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Engineer AI and Machine Learning</t>
+          <t>SENIOR COMPUTER VISION ENGINEER – REMOTE SENSING</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Satlantis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aurora, CO, US USA</t>
+          <t>Gainesville, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, LLaMA, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, FastAPI, Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ff0cfb22a83b3c4</t>
+          <t>https://www.indeed.com/viewjob?jk=74994cef74235bca</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Associate Software Engineer, Platform – COCore</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Glue, Redshift, Data Lake, CI/CD, Git, Redshift, R, Scala</t>
+          <t>RAG, Copilot, S3, EC2, Athena, Terraform, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,19 +881,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50effdd5410c6590</t>
+          <t>https://www.indeed.com/viewjob?jk=99ed0d4d942ded9c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Commercial Data Analyst</t>
+          <t>AI &amp; Cloud Platform Consultant Expert</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bonterra</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, AKS, Git, Tableau, Power BI, Quicksight, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8de79a6d9da6728</t>
+          <t>https://www.indeed.com/viewjob?jk=03afdcd6cea2e3b1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer, Control Plane</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Aerospike</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1566b51c5ab7b9</t>
+          <t>https://www.indeed.com/viewjob?jk=23d6e1a2ca383519</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Intern</t>
+          <t>Generative AI Engineer - Demand Science Portfolio</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CNX</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Canonsburg, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Data Lake, Git, Snowflake, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5cfd4d75c45f55</t>
+          <t>https://www.indeed.com/viewjob?jk=6c974f5ee79fc891</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Avaya</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, AWS SageMaker, Redshift, Git, Redshift, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93cc248964e1485d</t>
+          <t>https://www.indeed.com/viewjob?jk=18bef1f99ab23901</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EasyPost</t>
+          <t>Kargo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Git, Kafka, NoSQL, Python, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, Copilot, Pinecone, Prompt Engineering, Kubernetes, CI/CD, Snowflake, Python, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d6509dfd302acb</t>
+          <t>https://www.indeed.com/viewjob?jk=151f42b85fb197aa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Graduate Engineer, Design Automation, Front-End &amp; AI Driven Methodologies</t>
+          <t>Senior Software Engineer - API Solutions</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Arm</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, TensorFlow, PyTorch, AKS, CI/CD, Git, Python, R, Scala</t>
+          <t>RAG, Athena, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dc49d90bae64d48</t>
+          <t>https://www.indeed.com/viewjob?jk=7bcf2915fd9bd1ef</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Integration Engineer 3</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Docker, CI/CD, Git, Hadoop, MongoDB, NoSQL, Python, SQL, R</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5cea9e989f2b26</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f481b0e2336aa7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,42 +1161,182 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fceeafafff1abbc</t>
+          <t>https://www.indeed.com/viewjob?jk=963466953e09c5cf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>AI Software Development Engineer in Test</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Intellibee Inc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, spaCy, NLTK, S3, Docker, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b98fe227204e83a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI Product Engineer (Full-Stack/ Prototyping Focus)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cydcor</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Agoura Hills, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Pinecone, FastAPI, CI/CD, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa17256b84dcfac7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Data Engineer</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>FanDuel</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>10</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Data Scientist, CI/CD, Databricks, Kafka, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, CI/CD, Git, Kafka, Matplotlib, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Full-Stack AI Application Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, CI/CD, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26faa0e635e5e3d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Program Integrity Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CareSource</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Snowflake, Databricks, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc2bdaa5742adddf</t>
         </is>
       </c>
     </row>
